--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J496"/>
+  <dimension ref="A1:J497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18298,6 +18298,42 @@
       <c r="J496" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>326.46</v>
+      </c>
+      <c r="C497" t="n">
+        <v>311.93</v>
+      </c>
+      <c r="D497" t="n">
+        <v>306.7</v>
+      </c>
+      <c r="E497" t="n">
+        <v>326.63</v>
+      </c>
+      <c r="F497" t="n">
+        <v>329.93</v>
+      </c>
+      <c r="G497" t="n">
+        <v>329.42</v>
+      </c>
+      <c r="H497" t="n">
+        <v>329.34</v>
+      </c>
+      <c r="I497" t="n">
+        <v>324.95</v>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18312,7 +18348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B566"/>
+  <dimension ref="A1:B567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23975,6 +24011,16 @@
       </c>
       <c r="B566" t="n">
         <v>0.46</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -24143,28 +24189,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09261387247243029</v>
+        <v>-0.09259844861626763</v>
       </c>
       <c r="J2" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K2" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01762822729844782</v>
+        <v>0.01770193467326586</v>
       </c>
       <c r="M2" t="n">
-        <v>4.156672078971945</v>
+        <v>4.148380076762936</v>
       </c>
       <c r="N2" t="n">
-        <v>26.29440170218744</v>
+        <v>26.24139165319728</v>
       </c>
       <c r="O2" t="n">
-        <v>5.127806714589332</v>
+        <v>5.122635225467189</v>
       </c>
       <c r="P2" t="n">
-        <v>328.8671492075183</v>
+        <v>328.8669909464514</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24221,28 +24267,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2941311196605027</v>
+        <v>-0.2937927513745633</v>
       </c>
       <c r="J3" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K3" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1314021874910309</v>
+        <v>0.1316574697770065</v>
       </c>
       <c r="M3" t="n">
-        <v>4.549459922768363</v>
+        <v>4.542398618302255</v>
       </c>
       <c r="N3" t="n">
-        <v>31.45879338004239</v>
+        <v>31.39674371751425</v>
       </c>
       <c r="O3" t="n">
-        <v>5.608813901355829</v>
+        <v>5.603279728651271</v>
       </c>
       <c r="P3" t="n">
-        <v>318.8563460801994</v>
+        <v>318.8528741516908</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24299,28 +24345,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3142568751715144</v>
+        <v>-0.3147564095504789</v>
       </c>
       <c r="J4" t="n">
+        <v>496</v>
+      </c>
+      <c r="K4" t="n">
         <v>495</v>
       </c>
-      <c r="K4" t="n">
-        <v>494</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1926047970244708</v>
+        <v>0.1937956174846085</v>
       </c>
       <c r="M4" t="n">
-        <v>3.835827248526558</v>
+        <v>3.829874273485282</v>
       </c>
       <c r="N4" t="n">
-        <v>22.6263572966756</v>
+        <v>22.58361665761132</v>
       </c>
       <c r="O4" t="n">
-        <v>4.756717071329301</v>
+        <v>4.752222286216346</v>
       </c>
       <c r="P4" t="n">
-        <v>316.202747222856</v>
+        <v>316.2078973553098</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24381,28 +24427,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1196871893410584</v>
+        <v>-0.1203036530732501</v>
       </c>
       <c r="J5" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K5" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04962198037315635</v>
+        <v>0.05031278749421564</v>
       </c>
       <c r="M5" t="n">
-        <v>2.966916121183598</v>
+        <v>2.963626694609085</v>
       </c>
       <c r="N5" t="n">
-        <v>15.09251443987602</v>
+        <v>15.06665098375475</v>
       </c>
       <c r="O5" t="n">
-        <v>3.884908549744257</v>
+        <v>3.881578413964446</v>
       </c>
       <c r="P5" t="n">
-        <v>331.2927957676833</v>
+        <v>331.2991211772896</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24459,28 +24505,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06952737907458054</v>
+        <v>0.06909330009829501</v>
       </c>
       <c r="J6" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K6" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01913439693665731</v>
+        <v>0.01898275376459879</v>
       </c>
       <c r="M6" t="n">
-        <v>2.607976470526463</v>
+        <v>2.60510176619969</v>
       </c>
       <c r="N6" t="n">
-        <v>13.63171241322354</v>
+        <v>13.60649253223722</v>
       </c>
       <c r="O6" t="n">
-        <v>3.692114897077763</v>
+        <v>3.688697945378182</v>
       </c>
       <c r="P6" t="n">
-        <v>329.1590252236195</v>
+        <v>329.1634792201534</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24537,28 +24583,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2112387634558327</v>
+        <v>0.2113359407707384</v>
       </c>
       <c r="J7" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K7" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1150433884454837</v>
+        <v>0.115603967589874</v>
       </c>
       <c r="M7" t="n">
-        <v>3.325806411358068</v>
+        <v>3.319514075599049</v>
       </c>
       <c r="N7" t="n">
-        <v>18.88215329239624</v>
+        <v>18.84419787216498</v>
       </c>
       <c r="O7" t="n">
-        <v>4.345359972706087</v>
+        <v>4.340990425256082</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6113050301333</v>
+        <v>323.6103079133702</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24615,28 +24661,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3615335610533102</v>
+        <v>0.3614074206379958</v>
       </c>
       <c r="J8" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K8" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2594197082611071</v>
+        <v>0.2601645796968429</v>
       </c>
       <c r="M8" t="n">
-        <v>3.514147776093921</v>
+        <v>3.507701231682394</v>
       </c>
       <c r="N8" t="n">
-        <v>20.52628687060388</v>
+        <v>20.48509436010128</v>
       </c>
       <c r="O8" t="n">
-        <v>4.530594538314356</v>
+        <v>4.526046217185733</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1123408889383</v>
+        <v>320.1136351902137</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24693,28 +24739,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3717485827602131</v>
+        <v>0.3721116944548641</v>
       </c>
       <c r="J9" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K9" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2086472604276136</v>
+        <v>0.2097189323540554</v>
       </c>
       <c r="M9" t="n">
-        <v>3.875382621971935</v>
+        <v>3.869304595252633</v>
       </c>
       <c r="N9" t="n">
-        <v>28.83367765416761</v>
+        <v>28.77712906103141</v>
       </c>
       <c r="O9" t="n">
-        <v>5.369699959417436</v>
+        <v>5.364431848857008</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2562447740299</v>
+        <v>314.2525189584116</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24752,7 +24798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J496"/>
+  <dimension ref="A1:J497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50543,6 +50589,58 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-46.38323731209198,168.0094009774388</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-46.383116420635275,168.00853195590128</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-46.383011653142226,168.00781553024862</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-46.38280709210724,168.00701829238997</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-46.38250814573672,168.00621923672912</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-46.38219781664375,168.00544020170037</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-46.38188883930286,168.00464656786343</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>-46.381677820755655,168.00379059484143</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J497"/>
+  <dimension ref="A1:J499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18332,6 +18332,78 @@
         <v>324.95</v>
       </c>
       <c r="J497" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>326.7</v>
+      </c>
+      <c r="C498" t="n">
+        <v>312.54</v>
+      </c>
+      <c r="D498" t="n">
+        <v>307.11</v>
+      </c>
+      <c r="E498" t="n">
+        <v>326.58</v>
+      </c>
+      <c r="F498" t="n">
+        <v>329.81</v>
+      </c>
+      <c r="G498" t="n">
+        <v>328.88</v>
+      </c>
+      <c r="H498" t="n">
+        <v>328.72</v>
+      </c>
+      <c r="I498" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>327.52</v>
+      </c>
+      <c r="C499" t="n">
+        <v>313.48</v>
+      </c>
+      <c r="D499" t="n">
+        <v>308.69</v>
+      </c>
+      <c r="E499" t="n">
+        <v>327.29</v>
+      </c>
+      <c r="F499" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="G499" t="n">
+        <v>329.54</v>
+      </c>
+      <c r="H499" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="I499" t="n">
+        <v>323.23</v>
+      </c>
+      <c r="J499" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18348,7 +18420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B567"/>
+  <dimension ref="A1:B569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24021,6 +24093,26 @@
       </c>
       <c r="B567" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>
@@ -24189,28 +24281,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09259844861626763</v>
+        <v>-0.09204191834571655</v>
       </c>
       <c r="J2" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K2" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01770193467326586</v>
+        <v>0.01764886450212755</v>
       </c>
       <c r="M2" t="n">
-        <v>4.148380076762936</v>
+        <v>4.134886508482292</v>
       </c>
       <c r="N2" t="n">
-        <v>26.24139165319728</v>
+        <v>26.13855171353048</v>
       </c>
       <c r="O2" t="n">
-        <v>5.122635225467189</v>
+        <v>5.112587575145337</v>
       </c>
       <c r="P2" t="n">
-        <v>328.8669909464514</v>
+        <v>328.861270832509</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24267,28 +24359,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2937927513745633</v>
+        <v>-0.2922468107442309</v>
       </c>
       <c r="J3" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K3" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1316574697770065</v>
+        <v>0.1314351364446693</v>
       </c>
       <c r="M3" t="n">
-        <v>4.542398618302255</v>
+        <v>4.533736440737898</v>
       </c>
       <c r="N3" t="n">
-        <v>31.39674371751425</v>
+        <v>31.28603679492959</v>
       </c>
       <c r="O3" t="n">
-        <v>5.603279728651271</v>
+        <v>5.59339224397231</v>
       </c>
       <c r="P3" t="n">
-        <v>318.8528741516908</v>
+        <v>318.8369873212009</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24345,28 +24437,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3147564095504789</v>
+        <v>-0.3147557622525133</v>
       </c>
       <c r="J4" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K4" t="n">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1937956174846085</v>
+        <v>0.1952069550205352</v>
       </c>
       <c r="M4" t="n">
-        <v>3.829874273485282</v>
+        <v>3.817650557539285</v>
       </c>
       <c r="N4" t="n">
-        <v>22.58361665761132</v>
+        <v>22.49526183844188</v>
       </c>
       <c r="O4" t="n">
-        <v>4.752222286216346</v>
+        <v>4.742917017874325</v>
       </c>
       <c r="P4" t="n">
-        <v>316.2078973553098</v>
+        <v>316.2078875351594</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24427,28 +24519,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1203036530732501</v>
+        <v>-0.1212639813006618</v>
       </c>
       <c r="J5" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K5" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05031278749421564</v>
+        <v>0.05150089403358826</v>
       </c>
       <c r="M5" t="n">
-        <v>2.963626694609085</v>
+        <v>2.955889102122188</v>
       </c>
       <c r="N5" t="n">
-        <v>15.06665098375475</v>
+        <v>15.01225793106306</v>
       </c>
       <c r="O5" t="n">
-        <v>3.881578413964446</v>
+        <v>3.874565515133673</v>
       </c>
       <c r="P5" t="n">
-        <v>331.2991211772896</v>
+        <v>331.3089874000624</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24505,28 +24597,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06909330009829501</v>
+        <v>0.06846202860768906</v>
       </c>
       <c r="J6" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K6" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01898275376459879</v>
+        <v>0.01880695511254926</v>
       </c>
       <c r="M6" t="n">
-        <v>2.60510176619969</v>
+        <v>2.598105340214848</v>
       </c>
       <c r="N6" t="n">
-        <v>13.60649253223722</v>
+        <v>13.55488117497186</v>
       </c>
       <c r="O6" t="n">
-        <v>3.688697945378182</v>
+        <v>3.681695421266113</v>
       </c>
       <c r="P6" t="n">
-        <v>329.1634792201534</v>
+        <v>329.1699641690813</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24583,28 +24675,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2113359407707384</v>
+        <v>0.2113522575704708</v>
       </c>
       <c r="J7" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K7" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L7" t="n">
-        <v>0.115603967589874</v>
+        <v>0.1165508118070437</v>
       </c>
       <c r="M7" t="n">
-        <v>3.319514075599049</v>
+        <v>3.307504984091918</v>
       </c>
       <c r="N7" t="n">
-        <v>18.84419787216498</v>
+        <v>18.76896264238081</v>
       </c>
       <c r="O7" t="n">
-        <v>4.340990425256082</v>
+        <v>4.332316082926177</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6103079133702</v>
+        <v>323.6101389449832</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24661,28 +24753,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3614074206379958</v>
+        <v>0.3608259345315951</v>
       </c>
       <c r="J8" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K8" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2601645796968429</v>
+        <v>0.2612763018453262</v>
       </c>
       <c r="M8" t="n">
-        <v>3.507701231682394</v>
+        <v>3.49653753900231</v>
       </c>
       <c r="N8" t="n">
-        <v>20.48509436010128</v>
+        <v>20.4050524621909</v>
       </c>
       <c r="O8" t="n">
-        <v>4.526046217185733</v>
+        <v>4.517195198592916</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1136351902137</v>
+        <v>320.1196092973792</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24739,28 +24831,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3721116944548641</v>
+        <v>0.3718162371230069</v>
       </c>
       <c r="J9" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K9" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2097189323540554</v>
+        <v>0.2109574802099559</v>
       </c>
       <c r="M9" t="n">
-        <v>3.869304595252633</v>
+        <v>3.855778878906961</v>
       </c>
       <c r="N9" t="n">
-        <v>28.77712906103141</v>
+        <v>28.66304958012978</v>
       </c>
       <c r="O9" t="n">
-        <v>5.364431848857008</v>
+        <v>5.353788339123034</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2525189584116</v>
+        <v>314.2555567949603</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24798,7 +24890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J497"/>
+  <dimension ref="A1:J499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50641,6 +50733,110 @@
         </is>
       </c>
     </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:27:19+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-46.38323946731699,168.0094008921997</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-46.3831218740151,168.00853117764194</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-46.3830149904303,168.0078132783825</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-46.38280673190903,168.00701868015562</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-46.38250724100982,168.00622008371516</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-46.38219370759649,168.0054439275049</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-46.3818838082571,168.0046500208283</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-46.38167143846596,168.00379371449756</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-46.38324683100245,168.00940060096596</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-46.38313027758399,168.00852997835665</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-46.38302785119842,168.0078046004568</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-46.38281184672324,168.0070131738828</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-46.38251319712847,168.00621450772317</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-46.38219872976534,168.0054393737437</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-46.38188729753079,168.00464762603016</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-46.38166318403777,168.00379774925165</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J499"/>
+  <dimension ref="A1:J500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18406,6 +18406,42 @@
       <c r="J499" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>331.23</v>
+      </c>
+      <c r="C500" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="D500" t="n">
+        <v>312.53</v>
+      </c>
+      <c r="E500" t="n">
+        <v>327.74</v>
+      </c>
+      <c r="F500" t="n">
+        <v>328.51</v>
+      </c>
+      <c r="G500" t="n">
+        <v>326.37</v>
+      </c>
+      <c r="H500" t="n">
+        <v>326.08</v>
+      </c>
+      <c r="I500" t="n">
+        <v>321.27</v>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B569"/>
+  <dimension ref="A1:B570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24113,6 +24149,16 @@
       </c>
       <c r="B569" t="n">
         <v>0.31</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>-0.76</v>
       </c>
     </row>
   </sheetData>
@@ -24281,28 +24327,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09204191834571655</v>
+        <v>-0.0900714180583108</v>
       </c>
       <c r="J2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K2" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01764886450212755</v>
+        <v>0.01696203473919755</v>
       </c>
       <c r="M2" t="n">
-        <v>4.134886508482292</v>
+        <v>4.137626929347155</v>
       </c>
       <c r="N2" t="n">
-        <v>26.13855171353048</v>
+        <v>26.13237794988671</v>
       </c>
       <c r="O2" t="n">
-        <v>5.112587575145337</v>
+        <v>5.111983758765936</v>
       </c>
       <c r="P2" t="n">
-        <v>328.861270832509</v>
+        <v>328.8408441792882</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24359,28 +24405,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2922468107442309</v>
+        <v>-0.2892057330991623</v>
       </c>
       <c r="J3" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K3" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1314351364446693</v>
+        <v>0.1291934744360663</v>
       </c>
       <c r="M3" t="n">
-        <v>4.533736440737898</v>
+        <v>4.543367512481447</v>
       </c>
       <c r="N3" t="n">
-        <v>31.28603679492959</v>
+        <v>31.33339695651694</v>
       </c>
       <c r="O3" t="n">
-        <v>5.59339224397231</v>
+        <v>5.597624224304177</v>
       </c>
       <c r="P3" t="n">
-        <v>318.8369873212009</v>
+        <v>318.8054628201033</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24437,28 +24483,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3147557622525133</v>
+        <v>-0.3128250666885145</v>
       </c>
       <c r="J4" t="n">
+        <v>499</v>
+      </c>
+      <c r="K4" t="n">
         <v>498</v>
       </c>
-      <c r="K4" t="n">
-        <v>497</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1952069550205352</v>
+        <v>0.1937051797722597</v>
       </c>
       <c r="M4" t="n">
-        <v>3.817650557539285</v>
+        <v>3.821904320969137</v>
       </c>
       <c r="N4" t="n">
-        <v>22.49526183844188</v>
+        <v>22.4940308335745</v>
       </c>
       <c r="O4" t="n">
-        <v>4.742917017874325</v>
+        <v>4.742787243127663</v>
       </c>
       <c r="P4" t="n">
-        <v>316.2078875351594</v>
+        <v>316.1877789747263</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24519,28 +24565,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1212639813006618</v>
+        <v>-0.1214055977412748</v>
       </c>
       <c r="J5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05150089403358826</v>
+        <v>0.05184281989609874</v>
       </c>
       <c r="M5" t="n">
-        <v>2.955889102122188</v>
+        <v>2.950565154461439</v>
       </c>
       <c r="N5" t="n">
-        <v>15.01225793106306</v>
+        <v>14.98241191289343</v>
       </c>
       <c r="O5" t="n">
-        <v>3.874565515133673</v>
+        <v>3.870712067939623</v>
       </c>
       <c r="P5" t="n">
-        <v>331.3089874000624</v>
+        <v>331.3104554282283</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24597,28 +24643,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06846202860768906</v>
+        <v>0.06744784691618007</v>
       </c>
       <c r="J6" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K6" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01880695511254926</v>
+        <v>0.01833143037819818</v>
       </c>
       <c r="M6" t="n">
-        <v>2.598105340214848</v>
+        <v>2.598455540679774</v>
       </c>
       <c r="N6" t="n">
-        <v>13.55488117497186</v>
+        <v>13.53995751436072</v>
       </c>
       <c r="O6" t="n">
-        <v>3.681695421266113</v>
+        <v>3.679668125573381</v>
       </c>
       <c r="P6" t="n">
-        <v>329.1699641690813</v>
+        <v>329.1804774066827</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24675,28 +24721,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2113522575704708</v>
+        <v>0.2101800537074442</v>
       </c>
       <c r="J7" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K7" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1165508118070437</v>
+        <v>0.1157975259452563</v>
       </c>
       <c r="M7" t="n">
-        <v>3.307504984091918</v>
+        <v>3.307378775995981</v>
       </c>
       <c r="N7" t="n">
-        <v>18.76896264238081</v>
+        <v>18.74770151178339</v>
       </c>
       <c r="O7" t="n">
-        <v>4.332316082926177</v>
+        <v>4.329861604229793</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6101389449832</v>
+        <v>323.6222902762806</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24753,28 +24799,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3608259345315951</v>
+        <v>0.3593360052476469</v>
       </c>
       <c r="J8" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K8" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2612763018453262</v>
+        <v>0.2603292465568912</v>
       </c>
       <c r="M8" t="n">
-        <v>3.49653753900231</v>
+        <v>3.496865505730872</v>
       </c>
       <c r="N8" t="n">
-        <v>20.4050524621909</v>
+        <v>20.39057836154607</v>
       </c>
       <c r="O8" t="n">
-        <v>4.517195198592916</v>
+        <v>4.515592802893776</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1196092973792</v>
+        <v>320.1350542425035</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24831,28 +24877,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3718162371230069</v>
+        <v>0.3706373946511978</v>
       </c>
       <c r="J9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K9" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2109574802099559</v>
+        <v>0.2105799472676223</v>
       </c>
       <c r="M9" t="n">
-        <v>3.855778878906961</v>
+        <v>3.854001751911238</v>
       </c>
       <c r="N9" t="n">
-        <v>28.66304958012978</v>
+        <v>28.62214635912647</v>
       </c>
       <c r="O9" t="n">
-        <v>5.353788339123034</v>
+        <v>5.349966949348984</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2555567949603</v>
+        <v>314.2677769435832</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24890,7 +24936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J499"/>
+  <dimension ref="A1:J500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50837,6 +50883,58 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-46.383280147188934,168.00939928330897</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-46.38317515621729,168.00852357365488</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-46.38305910774525,168.00778350978413</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-46.382815088506725,168.00700968399107</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-46.38249743980122,168.00622925939552</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-46.38217460813423,168.00546124558878</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-46.381862385738216,168.00466472376792</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-46.381646504986406,168.00380590194663</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J500"/>
+  <dimension ref="A1:J501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18442,6 +18442,42 @@
       <c r="J500" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>333.54</v>
+      </c>
+      <c r="C501" t="n">
+        <v>320.65</v>
+      </c>
+      <c r="D501" t="n">
+        <v>314.31</v>
+      </c>
+      <c r="E501" t="n">
+        <v>329.11</v>
+      </c>
+      <c r="F501" t="n">
+        <v>329.48</v>
+      </c>
+      <c r="G501" t="n">
+        <v>327.36</v>
+      </c>
+      <c r="H501" t="n">
+        <v>327.54</v>
+      </c>
+      <c r="I501" t="n">
+        <v>322.56</v>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -18456,7 +18492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B570"/>
+  <dimension ref="A1:B571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24159,6 +24195,16 @@
       </c>
       <c r="B570" t="n">
         <v>-0.76</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -24327,28 +24373,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0900714180583108</v>
+        <v>-0.08718083924109772</v>
       </c>
       <c r="J2" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K2" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01696203473919755</v>
+        <v>0.01592043276450816</v>
       </c>
       <c r="M2" t="n">
-        <v>4.137626929347155</v>
+        <v>4.14563490423199</v>
       </c>
       <c r="N2" t="n">
-        <v>26.13237794988671</v>
+        <v>26.18029015933275</v>
       </c>
       <c r="O2" t="n">
-        <v>5.111983758765936</v>
+        <v>5.116667876590462</v>
       </c>
       <c r="P2" t="n">
-        <v>328.8408441792882</v>
+        <v>328.81085248754</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24405,28 +24451,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2892057330991623</v>
+        <v>-0.2853212640292774</v>
       </c>
       <c r="J3" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K3" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1291934744360663</v>
+        <v>0.1260565297856601</v>
       </c>
       <c r="M3" t="n">
-        <v>4.543367512481447</v>
+        <v>4.558559067046397</v>
       </c>
       <c r="N3" t="n">
-        <v>31.33339695651694</v>
+        <v>31.45163974680079</v>
       </c>
       <c r="O3" t="n">
-        <v>5.597624224304177</v>
+        <v>5.608176151548807</v>
       </c>
       <c r="P3" t="n">
-        <v>318.8054628201033</v>
+        <v>318.765158851135</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24483,28 +24529,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3128250666885145</v>
+        <v>-0.3101842926318621</v>
       </c>
       <c r="J4" t="n">
+        <v>500</v>
+      </c>
+      <c r="K4" t="n">
         <v>499</v>
       </c>
-      <c r="K4" t="n">
-        <v>498</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1937051797722597</v>
+        <v>0.1912206054325485</v>
       </c>
       <c r="M4" t="n">
-        <v>3.821904320969137</v>
+        <v>3.830503526102538</v>
       </c>
       <c r="N4" t="n">
-        <v>22.4940308335745</v>
+        <v>22.5317734496587</v>
       </c>
       <c r="O4" t="n">
-        <v>4.742787243127663</v>
+        <v>4.746764524353268</v>
       </c>
       <c r="P4" t="n">
-        <v>316.1877789747263</v>
+        <v>316.1602499013587</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24565,28 +24611,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1214055977412748</v>
+        <v>-0.1209872444991782</v>
       </c>
       <c r="J5" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K5" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05184281989609874</v>
+        <v>0.0517246357508101</v>
       </c>
       <c r="M5" t="n">
-        <v>2.950565154461439</v>
+        <v>2.946983646115675</v>
       </c>
       <c r="N5" t="n">
-        <v>14.98241191289343</v>
+        <v>14.9545454709021</v>
       </c>
       <c r="O5" t="n">
-        <v>3.870712067939623</v>
+        <v>3.867110739415422</v>
       </c>
       <c r="P5" t="n">
-        <v>331.3104554282283</v>
+        <v>331.3061147330693</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24643,28 +24689,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06744784691618007</v>
+        <v>0.06683776961281677</v>
       </c>
       <c r="J6" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K6" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01833143037819818</v>
+        <v>0.01808357143283523</v>
       </c>
       <c r="M6" t="n">
-        <v>2.598455540679774</v>
+        <v>2.596612491597047</v>
       </c>
       <c r="N6" t="n">
-        <v>13.53995751436072</v>
+        <v>13.51733999398532</v>
       </c>
       <c r="O6" t="n">
-        <v>3.679668125573381</v>
+        <v>3.676593531244013</v>
       </c>
       <c r="P6" t="n">
-        <v>329.1804774066827</v>
+        <v>329.1868073674214</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24721,28 +24767,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2101800537074442</v>
+        <v>0.2094210175965666</v>
       </c>
       <c r="J7" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K7" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1157975259452563</v>
+        <v>0.1154940078641313</v>
       </c>
       <c r="M7" t="n">
-        <v>3.307378775995981</v>
+        <v>3.304958415658505</v>
       </c>
       <c r="N7" t="n">
-        <v>18.74770151178339</v>
+        <v>18.71711364410106</v>
       </c>
       <c r="O7" t="n">
-        <v>4.329861604229793</v>
+        <v>4.326327963076894</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6222902762806</v>
+        <v>323.6301657844411</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24799,28 +24845,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3593360052476469</v>
+        <v>0.3584556823278764</v>
       </c>
       <c r="J8" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K8" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2603292465568912</v>
+        <v>0.2601896547951128</v>
       </c>
       <c r="M8" t="n">
-        <v>3.496865505730872</v>
+        <v>3.494188536757071</v>
       </c>
       <c r="N8" t="n">
-        <v>20.39057836154607</v>
+        <v>20.35908862838178</v>
       </c>
       <c r="O8" t="n">
-        <v>4.515592802893776</v>
+        <v>4.512104678349316</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1350542425035</v>
+        <v>320.1441881825613</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24877,28 +24923,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3706373946511978</v>
+        <v>0.3699957434051658</v>
       </c>
       <c r="J9" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K9" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2105799472676223</v>
+        <v>0.2107460549755593</v>
       </c>
       <c r="M9" t="n">
-        <v>3.854001751911238</v>
+        <v>3.849530284156152</v>
       </c>
       <c r="N9" t="n">
-        <v>28.62214635912647</v>
+        <v>28.56983830705601</v>
       </c>
       <c r="O9" t="n">
-        <v>5.349966949348984</v>
+        <v>5.34507608056761</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2677769435832</v>
+        <v>314.2744345051299</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24936,7 +24982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J500"/>
+  <dimension ref="A1:J501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50935,6 +50981,58 @@
         </is>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-46.38330089122948,168.00939846287937</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-46.38319437714557,168.00852083060119</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-46.3830735964554,168.00777373336996</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-46.382824957935725,168.00699905920692</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-46.38250475301081,168.00622241292666</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-46.38218214138865,168.0054544149516</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-46.38187423304063,168.00465659259828</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-46.381657482525405,168.0038005361429</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J501"/>
+  <dimension ref="A1:J502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18476,6 +18476,42 @@
         <v>322.56</v>
       </c>
       <c r="J501" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>334.88</v>
+      </c>
+      <c r="C502" t="n">
+        <v>322.26</v>
+      </c>
+      <c r="D502" t="n">
+        <v>316.58</v>
+      </c>
+      <c r="E502" t="n">
+        <v>330.63</v>
+      </c>
+      <c r="F502" t="n">
+        <v>330.68</v>
+      </c>
+      <c r="G502" t="n">
+        <v>328.24</v>
+      </c>
+      <c r="H502" t="n">
+        <v>328.59</v>
+      </c>
+      <c r="I502" t="n">
+        <v>322.94</v>
+      </c>
+      <c r="J502" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -18492,7 +18528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B571"/>
+  <dimension ref="A1:B572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24205,6 +24241,16 @@
       </c>
       <c r="B571" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -24373,28 +24419,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08718083924109772</v>
+        <v>-0.08377183012947365</v>
       </c>
       <c r="J2" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K2" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01592043276450816</v>
+        <v>0.01470746273134238</v>
       </c>
       <c r="M2" t="n">
-        <v>4.14563490423199</v>
+        <v>4.15655422954051</v>
       </c>
       <c r="N2" t="n">
-        <v>26.18029015933275</v>
+        <v>26.26786455066334</v>
       </c>
       <c r="O2" t="n">
-        <v>5.116667876590462</v>
+        <v>5.12521848809037</v>
       </c>
       <c r="P2" t="n">
-        <v>328.81085248754</v>
+        <v>328.77541729671</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24451,28 +24497,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2853212640292774</v>
+        <v>-0.2808108960604596</v>
       </c>
       <c r="J3" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K3" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1260565297856601</v>
+        <v>0.1222505090654474</v>
       </c>
       <c r="M3" t="n">
-        <v>4.558559067046397</v>
+        <v>4.57766422334442</v>
       </c>
       <c r="N3" t="n">
-        <v>31.45163974680079</v>
+        <v>31.6336383473707</v>
       </c>
       <c r="O3" t="n">
-        <v>5.608176151548807</v>
+        <v>5.624378929923792</v>
       </c>
       <c r="P3" t="n">
-        <v>318.765158851135</v>
+        <v>318.7182755063108</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24529,28 +24575,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3101842926318621</v>
+        <v>-0.3066347684881011</v>
       </c>
       <c r="J4" t="n">
+        <v>501</v>
+      </c>
+      <c r="K4" t="n">
         <v>500</v>
       </c>
-      <c r="K4" t="n">
-        <v>499</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1912206054325485</v>
+        <v>0.1873798840086124</v>
       </c>
       <c r="M4" t="n">
-        <v>3.830503526102538</v>
+        <v>3.844582031718309</v>
       </c>
       <c r="N4" t="n">
-        <v>22.5317734496587</v>
+        <v>22.63687519284181</v>
       </c>
       <c r="O4" t="n">
-        <v>4.746764524353268</v>
+        <v>4.757822526412877</v>
       </c>
       <c r="P4" t="n">
-        <v>316.1602499013587</v>
+        <v>316.1231804273919</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24611,28 +24657,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1209872444991782</v>
+        <v>-0.1199524040804342</v>
       </c>
       <c r="J5" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K5" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0517246357508101</v>
+        <v>0.05107081172362793</v>
       </c>
       <c r="M5" t="n">
-        <v>2.946983646115675</v>
+        <v>2.946808530202846</v>
       </c>
       <c r="N5" t="n">
-        <v>14.9545454709021</v>
+        <v>14.93758131028135</v>
       </c>
       <c r="O5" t="n">
-        <v>3.867110739415422</v>
+        <v>3.864916727470509</v>
       </c>
       <c r="P5" t="n">
-        <v>331.3061147330693</v>
+        <v>331.2953580097762</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24689,28 +24735,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06683776961281677</v>
+        <v>0.06671935636433457</v>
       </c>
       <c r="J6" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K6" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01808357143283523</v>
+        <v>0.0181026502680155</v>
       </c>
       <c r="M6" t="n">
-        <v>2.596612491597047</v>
+        <v>2.592077032921448</v>
       </c>
       <c r="N6" t="n">
-        <v>13.51733999398532</v>
+        <v>13.49052798746474</v>
       </c>
       <c r="O6" t="n">
-        <v>3.676593531244013</v>
+        <v>3.672945410357297</v>
       </c>
       <c r="P6" t="n">
-        <v>329.1868073674214</v>
+        <v>329.1880382224644</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24767,28 +24813,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2094210175965666</v>
+        <v>0.2090258507048632</v>
       </c>
       <c r="J7" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K7" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1154940078641313</v>
+        <v>0.1155711388336883</v>
       </c>
       <c r="M7" t="n">
-        <v>3.304958415658505</v>
+        <v>3.300533254210595</v>
       </c>
       <c r="N7" t="n">
-        <v>18.71711364410106</v>
+        <v>18.68163304835941</v>
       </c>
       <c r="O7" t="n">
-        <v>4.326327963076894</v>
+        <v>4.322225474030642</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6301657844411</v>
+        <v>323.6342733751687</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24845,28 +24891,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3584556823278764</v>
+        <v>0.3580038842180162</v>
       </c>
       <c r="J8" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K8" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2601896547951128</v>
+        <v>0.2605728176213414</v>
       </c>
       <c r="M8" t="n">
-        <v>3.494188536757071</v>
+        <v>3.489416435785334</v>
       </c>
       <c r="N8" t="n">
-        <v>20.35908862838178</v>
+        <v>20.32090775839759</v>
       </c>
       <c r="O8" t="n">
-        <v>4.512104678349316</v>
+        <v>4.507871754874754</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1441881825613</v>
+        <v>320.1488844305663</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24923,28 +24969,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3699957434051658</v>
+        <v>0.3695049435752944</v>
       </c>
       <c r="J9" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K9" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2107460549755593</v>
+        <v>0.2110583388338647</v>
       </c>
       <c r="M9" t="n">
-        <v>3.849530284156152</v>
+        <v>3.84430824335757</v>
       </c>
       <c r="N9" t="n">
-        <v>28.56983830705601</v>
+        <v>28.51571105464248</v>
       </c>
       <c r="O9" t="n">
-        <v>5.34507608056761</v>
+        <v>5.340010398364639</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2744345051299</v>
+        <v>314.2795361593236</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -24982,7 +25028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J501"/>
+  <dimension ref="A1:J502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51033,6 +51079,58 @@
         </is>
       </c>
     </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-19 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>-46.38331292456899,168.00939798695856</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>-46.38320877049177,168.00851877649887</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>-46.38309207362913,168.00776126568783</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>-46.38283590795776,168.00698727112064</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>-46.38251380027971,168.0062139430657</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>-46.38218883761439,168.0054483432725</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>-46.381882753360394,168.00465074483697</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>-46.381660716218995,168.0037989555181</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J502"/>
+  <dimension ref="A1:J505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18514,6 +18514,114 @@
       <c r="J502" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>334.23</v>
+      </c>
+      <c r="C503" t="n">
+        <v>321.16</v>
+      </c>
+      <c r="D503" t="n">
+        <v>317.21</v>
+      </c>
+      <c r="E503" t="n">
+        <v>331.17</v>
+      </c>
+      <c r="F503" t="n">
+        <v>330.32</v>
+      </c>
+      <c r="G503" t="n">
+        <v>328.64</v>
+      </c>
+      <c r="H503" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="I503" t="n">
+        <v>323.21</v>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>332.43</v>
+      </c>
+      <c r="C504" t="n">
+        <v>320.84</v>
+      </c>
+      <c r="D504" t="n">
+        <v>317.48</v>
+      </c>
+      <c r="E504" t="n">
+        <v>332.46</v>
+      </c>
+      <c r="F504" t="n">
+        <v>331.61</v>
+      </c>
+      <c r="G504" t="n">
+        <v>330.04</v>
+      </c>
+      <c r="H504" t="n">
+        <v>330.59</v>
+      </c>
+      <c r="I504" t="n">
+        <v>324.56</v>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>330.68</v>
+      </c>
+      <c r="C505" t="n">
+        <v>318.9</v>
+      </c>
+      <c r="D505" t="n">
+        <v>316.74</v>
+      </c>
+      <c r="E505" t="n">
+        <v>331.89</v>
+      </c>
+      <c r="F505" t="n">
+        <v>331.18</v>
+      </c>
+      <c r="G505" t="n">
+        <v>328.94</v>
+      </c>
+      <c r="H505" t="n">
+        <v>329.58</v>
+      </c>
+      <c r="I505" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -18528,7 +18636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B572"/>
+  <dimension ref="A1:B575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24251,6 +24359,36 @@
       </c>
       <c r="B572" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -24419,28 +24557,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08377183012947365</v>
+        <v>-0.07661589383690108</v>
       </c>
       <c r="J2" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K2" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01470746273134238</v>
+        <v>0.01240188354348826</v>
       </c>
       <c r="M2" t="n">
-        <v>4.15655422954051</v>
+        <v>4.172506764710005</v>
       </c>
       <c r="N2" t="n">
-        <v>26.26786455066334</v>
+        <v>26.32854274499612</v>
       </c>
       <c r="O2" t="n">
-        <v>5.12521848809037</v>
+        <v>5.131134644987998</v>
       </c>
       <c r="P2" t="n">
-        <v>328.77541729671</v>
+        <v>328.700602733803</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24497,28 +24635,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2808108960604596</v>
+        <v>-0.2697919639934134</v>
       </c>
       <c r="J3" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K3" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1222505090654474</v>
+        <v>0.1137687732311056</v>
       </c>
       <c r="M3" t="n">
-        <v>4.57766422334442</v>
+        <v>4.618648994135508</v>
       </c>
       <c r="N3" t="n">
-        <v>31.6336383473707</v>
+        <v>31.93584894884606</v>
       </c>
       <c r="O3" t="n">
-        <v>5.624378929923792</v>
+        <v>5.651181199434864</v>
       </c>
       <c r="P3" t="n">
-        <v>318.7182755063108</v>
+        <v>318.6030545441888</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24575,28 +24713,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3066347684881011</v>
+        <v>-0.295392140498265</v>
       </c>
       <c r="J4" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K4" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1873798840086124</v>
+        <v>0.1751216798658043</v>
       </c>
       <c r="M4" t="n">
-        <v>3.844582031718309</v>
+        <v>3.890318416261664</v>
       </c>
       <c r="N4" t="n">
-        <v>22.63687519284181</v>
+        <v>23.00200007158687</v>
       </c>
       <c r="O4" t="n">
-        <v>4.757822526412877</v>
+        <v>4.796040040657174</v>
       </c>
       <c r="P4" t="n">
-        <v>316.1231804273919</v>
+        <v>316.0050608475945</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24657,28 +24795,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1199524040804342</v>
+        <v>-0.1154033441102662</v>
       </c>
       <c r="J5" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K5" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05107081172362793</v>
+        <v>0.0478304575398496</v>
       </c>
       <c r="M5" t="n">
-        <v>2.946808530202846</v>
+        <v>2.954366732867212</v>
       </c>
       <c r="N5" t="n">
-        <v>14.93758131028135</v>
+        <v>14.93286058227264</v>
       </c>
       <c r="O5" t="n">
-        <v>3.864916727470509</v>
+        <v>3.864305963853359</v>
       </c>
       <c r="P5" t="n">
-        <v>331.2953580097762</v>
+        <v>331.2477801778109</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24735,28 +24873,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06671935636433457</v>
+        <v>0.06679475004265478</v>
       </c>
       <c r="J6" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K6" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0181026502680155</v>
+        <v>0.01839192890410013</v>
       </c>
       <c r="M6" t="n">
-        <v>2.592077032921448</v>
+        <v>2.579555248112949</v>
       </c>
       <c r="N6" t="n">
-        <v>13.49052798746474</v>
+        <v>13.41195142645963</v>
       </c>
       <c r="O6" t="n">
-        <v>3.672945410357297</v>
+        <v>3.662233120168572</v>
       </c>
       <c r="P6" t="n">
-        <v>329.1880382224644</v>
+        <v>329.1872441107566</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24813,28 +24951,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2090258507048632</v>
+        <v>0.2089861905575476</v>
       </c>
       <c r="J7" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K7" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1155711388336883</v>
+        <v>0.116960480769969</v>
       </c>
       <c r="M7" t="n">
-        <v>3.300533254210595</v>
+        <v>3.284286477811669</v>
       </c>
       <c r="N7" t="n">
-        <v>18.68163304835941</v>
+        <v>18.57259752355638</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322225474030642</v>
+        <v>4.309593661072513</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6342733751687</v>
+        <v>323.6346852702451</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -24891,28 +25029,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3580038842180162</v>
+        <v>0.3580930858555424</v>
       </c>
       <c r="J8" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K8" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2605728176213414</v>
+        <v>0.2633617318021656</v>
       </c>
       <c r="M8" t="n">
-        <v>3.489416435785334</v>
+        <v>3.471549093476533</v>
       </c>
       <c r="N8" t="n">
-        <v>20.32090775839759</v>
+        <v>20.20179460519893</v>
       </c>
       <c r="O8" t="n">
-        <v>4.507871754874754</v>
+        <v>4.494640653622816</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1488844305663</v>
+        <v>320.1479490389951</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -24969,28 +25107,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3695049435752944</v>
+        <v>0.3690177717565079</v>
       </c>
       <c r="J9" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K9" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2110583388338647</v>
+        <v>0.2129424875907185</v>
       </c>
       <c r="M9" t="n">
-        <v>3.84430824335757</v>
+        <v>3.825325709874739</v>
       </c>
       <c r="N9" t="n">
-        <v>28.51571105464248</v>
+        <v>28.34883279264372</v>
       </c>
       <c r="O9" t="n">
-        <v>5.340010398364639</v>
+        <v>5.324362195854422</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2795361593236</v>
+        <v>314.2846276991431</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25028,7 +25166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J502"/>
+  <dimension ref="A1:J505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51131,6 +51269,162 @@
         </is>
       </c>
     </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>-46.38330708750132,168.00939821781571</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>-46.383198936528544,168.00852017992295</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>-46.38309720165501,168.00775780549253</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>-46.38283979809683,168.00698308324672</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>-46.382511086099115,168.00621648402426</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>-46.38219188135323,168.00544558341784</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>-46.38188851471925,168.0046467906354</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>-46.38166301384337,168.00379783244244</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>-46.3832909233139,168.00939885711193</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>-46.38319607573922,168.00852058819166</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>-46.383099399380356,168.0077563225515</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>-46.3828490912061,168.00697307887881</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>-46.38252081191259,168.00620737892143</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>-46.38220253443857,168.00543592392407</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>-46.38189898253985,168.00463960623873</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>-46.38167450196503,168.0037922170627</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>-46.38327520813165,168.00939947864916</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>-46.38317873220394,168.0085230633195</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>-46.38309337598493,168.00776038690813</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>-46.38284498494865,168.00697749941392</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>-46.38251756997486,168.0062104139561</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>-46.382194164157305,168.00544351352664</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>-46.3818907868044,168.00464523123173</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>-46.38166624753691,168.0037962518173</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0534/nzd0534.xlsx
+++ b/data/nzd0534/nzd0534.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J505"/>
+  <dimension ref="A1:J506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18620,6 +18620,42 @@
         <v>323.59</v>
       </c>
       <c r="J505" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>326.74</v>
+      </c>
+      <c r="C506" t="n">
+        <v>314.53</v>
+      </c>
+      <c r="D506" t="n">
+        <v>313.28</v>
+      </c>
+      <c r="E506" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="F506" t="n">
+        <v>330.64</v>
+      </c>
+      <c r="G506" t="n">
+        <v>328.87</v>
+      </c>
+      <c r="H506" t="n">
+        <v>330.23</v>
+      </c>
+      <c r="I506" t="n">
+        <v>323.93</v>
+      </c>
+      <c r="J506" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -18636,7 +18672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B575"/>
+  <dimension ref="A1:B576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24389,6 +24425,16 @@
       </c>
       <c r="B575" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -24557,28 +24603,28 @@
         <v>0.1654</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07661589383690108</v>
+        <v>-0.07657230584368226</v>
       </c>
       <c r="J2" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K2" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01240188354348826</v>
+        <v>0.01244542093987988</v>
       </c>
       <c r="M2" t="n">
-        <v>4.172506764710005</v>
+        <v>4.164491079828629</v>
       </c>
       <c r="N2" t="n">
-        <v>26.32854274499612</v>
+        <v>26.27642985408704</v>
       </c>
       <c r="O2" t="n">
-        <v>5.131134644987998</v>
+        <v>5.126054023719126</v>
       </c>
       <c r="P2" t="n">
-        <v>328.700602733803</v>
+        <v>328.7001447177509</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -24635,28 +24681,28 @@
         <v>0.1657</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2697919639934134</v>
+        <v>-0.268500540760664</v>
       </c>
       <c r="J3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K3" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1137687732311056</v>
+        <v>0.113211622785705</v>
       </c>
       <c r="M3" t="n">
-        <v>4.618648994135508</v>
+        <v>4.617575517099274</v>
       </c>
       <c r="N3" t="n">
-        <v>31.93584894884606</v>
+        <v>31.89265658794335</v>
       </c>
       <c r="O3" t="n">
-        <v>5.651181199434864</v>
+        <v>5.647358372544047</v>
       </c>
       <c r="P3" t="n">
-        <v>318.6030545441888</v>
+        <v>318.5894844638308</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -24713,28 +24759,28 @@
         <v>0.1069</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.295392140498265</v>
+        <v>-0.2932631236485141</v>
       </c>
       <c r="J4" t="n">
+        <v>505</v>
+      </c>
+      <c r="K4" t="n">
         <v>504</v>
       </c>
-      <c r="K4" t="n">
-        <v>503</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1751216798658043</v>
+        <v>0.1733787390422701</v>
       </c>
       <c r="M4" t="n">
-        <v>3.890318416261664</v>
+        <v>3.89566315863825</v>
       </c>
       <c r="N4" t="n">
-        <v>23.00200007158687</v>
+        <v>23.01033161149813</v>
       </c>
       <c r="O4" t="n">
-        <v>4.796040040657174</v>
+        <v>4.796908547335266</v>
       </c>
       <c r="P4" t="n">
-        <v>316.0050608475945</v>
+        <v>315.9825855383495</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -24795,28 +24841,28 @@
         <v>0.0876</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1154033441102662</v>
+        <v>-0.1141326197185575</v>
       </c>
       <c r="J5" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K5" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0478304575398496</v>
+        <v>0.04698335635422468</v>
       </c>
       <c r="M5" t="n">
-        <v>2.954366732867212</v>
+        <v>2.955483841195407</v>
       </c>
       <c r="N5" t="n">
-        <v>14.93286058227264</v>
+        <v>14.9227000331901</v>
       </c>
       <c r="O5" t="n">
-        <v>3.864305963853359</v>
+        <v>3.86299107340285</v>
       </c>
       <c r="P5" t="n">
-        <v>331.2477801778109</v>
+        <v>331.2344275977495</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -24873,28 +24919,28 @@
         <v>0.1179</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06679475004265478</v>
+        <v>0.06665564530812146</v>
       </c>
       <c r="J6" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K6" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01839192890410013</v>
+        <v>0.01840096964882898</v>
       </c>
       <c r="M6" t="n">
-        <v>2.579555248112949</v>
+        <v>2.575203865750274</v>
       </c>
       <c r="N6" t="n">
-        <v>13.41195142645963</v>
+        <v>13.3856256988227</v>
       </c>
       <c r="O6" t="n">
-        <v>3.662233120168572</v>
+        <v>3.658637136806915</v>
       </c>
       <c r="P6" t="n">
-        <v>329.1872441107566</v>
+        <v>329.1887058023059</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -24951,28 +24997,28 @@
         <v>0.0997</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2089861905575476</v>
+        <v>0.2088281885250506</v>
       </c>
       <c r="J7" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K7" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L7" t="n">
-        <v>0.116960480769969</v>
+        <v>0.1172871051163457</v>
       </c>
       <c r="M7" t="n">
-        <v>3.284286477811669</v>
+        <v>3.278636114802291</v>
       </c>
       <c r="N7" t="n">
-        <v>18.57259752355638</v>
+        <v>18.53612018222153</v>
       </c>
       <c r="O7" t="n">
-        <v>4.309593661072513</v>
+        <v>4.305359471893321</v>
       </c>
       <c r="P7" t="n">
-        <v>323.6346852702451</v>
+        <v>323.6363455317484</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25029,28 +25075,28 @@
         <v>0.1055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3580930858555424</v>
+        <v>0.3582690002745434</v>
       </c>
       <c r="J8" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K8" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2633617318021656</v>
+        <v>0.2644595672939691</v>
       </c>
       <c r="M8" t="n">
-        <v>3.471549093476533</v>
+        <v>3.465543550886944</v>
       </c>
       <c r="N8" t="n">
-        <v>20.20179460519893</v>
+        <v>20.16216302661944</v>
       </c>
       <c r="O8" t="n">
-        <v>4.494640653622816</v>
+        <v>4.490229729826686</v>
       </c>
       <c r="P8" t="n">
-        <v>320.1479490389951</v>
+        <v>320.1461005568387</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -25107,28 +25153,28 @@
         <v>0.0922</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3690177717565079</v>
+        <v>0.3688985549638596</v>
       </c>
       <c r="J9" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K9" t="n">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2129424875907185</v>
+        <v>0.2136195684105964</v>
       </c>
       <c r="M9" t="n">
-        <v>3.825325709874739</v>
+        <v>3.818338669927999</v>
       </c>
       <c r="N9" t="n">
-        <v>28.34883279264372</v>
+        <v>28.29286732862473</v>
       </c>
       <c r="O9" t="n">
-        <v>5.324362195854422</v>
+        <v>5.319103996785993</v>
       </c>
       <c r="P9" t="n">
-        <v>314.2846276991431</v>
+        <v>314.2858804112016</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -25166,7 +25212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J505"/>
+  <dimension ref="A1:J506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51425,6 +51471,58 @@
         </is>
       </c>
     </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>-46.38323982652117,168.00940087799316</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>-46.38313966454921,168.00852863872893</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>-46.38306521253899,168.00777939050914</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>-46.382840590532545,168.00698223016124</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>-46.38251349870408,168.00621422539444</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>-46.382193631503036,168.00544399650127</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-46.38189606128766,168.00464161118694</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>-46.38166914084164,168.00379483757357</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
